--- a/輸出檔/0414直播表格.xlsx
+++ b/輸出檔/0414直播表格.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,11 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +572,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" t="n">
         <v>599</v>
       </c>
@@ -604,7 +610,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" t="n">
         <v>499</v>
       </c>
@@ -642,7 +648,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" t="n">
         <v>590</v>
       </c>
@@ -680,7 +686,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" t="n">
         <v>1080</v>
       </c>
@@ -718,7 +724,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" t="n">
         <v>590</v>
       </c>
@@ -756,7 +762,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" t="n">
         <v>980</v>
       </c>
@@ -789,7 +795,7 @@
           <t>V領綁帶冰絲坑條針織外套上衣</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>白、杏、黑</t>
@@ -806,6 +812,7 @@
           <t>肩寬38 袖長20 袖寬19 胸寬35 全長48</t>
         </is>
       </c>
+      <c r="J9" s="2" t="n"/>
       <c r="K9" t="n">
         <v>318</v>
       </c>
@@ -831,7 +838,7 @@
 L.XL拿L</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" t="n">
         <v>599</v>
       </c>
@@ -992,7 +999,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -1012,7 +1019,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1032,7 +1039,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1052,7 +1059,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1072,7 +1079,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1092,7 +1099,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1107,7 +1114,7 @@
           <t>V領綁帶冰絲坑條針織外套上衣</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>白、杏、黑</t>
@@ -1134,7 +1141,7 @@
 L.XL拿L</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1232,7 +1239,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -1246,7 +1253,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1260,7 +1267,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1274,7 +1281,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1288,7 +1295,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1302,7 +1309,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1311,7 +1318,7 @@
           <t>V領綁帶冰絲坑條針織外套上衣</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>白、杏、黑</t>
@@ -1332,7 +1339,7 @@
 L.XL拿L</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1491,7 +1498,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" t="n">
         <v>599</v>
       </c>
@@ -1524,7 +1531,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" t="n">
         <v>499</v>
       </c>
@@ -1557,7 +1564,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" t="n">
         <v>590</v>
       </c>
@@ -1590,7 +1597,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" t="n">
         <v>1080</v>
       </c>
@@ -1623,7 +1630,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" t="n">
         <v>590</v>
       </c>
@@ -1656,7 +1663,7 @@
           <t>S-XL適合</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" t="n">
         <v>980</v>
       </c>
@@ -1684,7 +1691,7 @@
           <t>V領綁帶冰絲坑條針織外套上衣</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>白、杏、黑</t>
@@ -1696,6 +1703,7 @@
       <c r="H9" t="n">
         <v>293</v>
       </c>
+      <c r="I9" s="2" t="n"/>
       <c r="J9" t="n">
         <v>318</v>
       </c>
@@ -1721,7 +1729,7 @@
 L.XL拿L</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" t="n">
         <v>599</v>
       </c>
